--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486969_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486969_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.7884</v>
+        <v>8.2273</v>
       </c>
       <c r="E2" t="n">
-        <v>6.4467</v>
+        <v>6.8264</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3416</v>
+        <v>1.4009</v>
       </c>
       <c r="G2" t="n">
         <v>6.2098</v>
@@ -610,13 +610,13 @@
         <v>1.2321</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5261</v>
+        <v>-0.0871</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5928</v>
+        <v>-0.2132</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0668</v>
+        <v>0.126</v>
       </c>
       <c r="V2" t="n">
         <v>1.8993</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. PAZ VAZQUEZ</t>
+          <t>G. BLAT BAEZA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.4857</v>
+        <v>4.7061</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9941</v>
+        <v>2.4547</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4916</v>
+        <v>2.2513</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8786</v>
+        <v>2.4289</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4184</v>
+        <v>0.9898</v>
       </c>
       <c r="I3" t="n">
-        <v>1.297</v>
+        <v>1.4392</v>
       </c>
       <c r="J3" t="n">
-        <v>1.0067</v>
+        <v>2.6098</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.7294</v>
+        <v>0.8473000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>1.7361</v>
+        <v>1.7626</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1281</v>
+        <v>-0.1809</v>
       </c>
       <c r="N3" t="n">
-        <v>0.311</v>
+        <v>0.1425</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4391</v>
+        <v>-0.3234</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6427</v>
+        <v>1.2321</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6427</v>
+        <v>2.2588</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4839</v>
+        <v>1.2853</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5069</v>
+        <v>0.8716</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9769</v>
+        <v>0.4137</v>
       </c>
       <c r="V3" t="n">
-        <v>0.4805</v>
+        <v>-0.2402</v>
       </c>
       <c r="W3" t="n">
-        <v>0.4805</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. BLAT BAEZA</t>
+          <t>S. PAZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8644</v>
+        <v>4.2775</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7612</v>
+        <v>2.0527</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1031</v>
+        <v>2.2248</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4289</v>
+        <v>0.8786</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9898</v>
+        <v>-0.4184</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4392</v>
+        <v>1.297</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6098</v>
+        <v>1.0067</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8473000000000001</v>
+        <v>-0.7294</v>
       </c>
       <c r="L4" t="n">
-        <v>1.7626</v>
+        <v>1.7361</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1809</v>
+        <v>-0.1281</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1425</v>
+        <v>0.311</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3234</v>
+        <v>-0.4391</v>
       </c>
       <c r="P4" t="n">
-        <v>1.2321</v>
+        <v>1.6427</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2588</v>
+        <v>1.6427</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4436</v>
+        <v>1.2757</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1781</v>
+        <v>0.5655</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2655</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2402</v>
+        <v>0.4805</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.4805</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. GOMEZ BARRAL</t>
+          <t>K. JOHNSON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.6413</v>
+        <v>4.1307</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.0607</v>
+        <v>5.3467</v>
       </c>
       <c r="F5" t="n">
-        <v>5.7021</v>
+        <v>-1.216</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9121</v>
+        <v>3.7978</v>
       </c>
       <c r="H5" t="n">
-        <v>1.47</v>
+        <v>0.8272</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5579</v>
+        <v>2.9707</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.5883</v>
+        <v>6.2808</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7144</v>
+        <v>1.2687</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.3027</v>
+        <v>5.0122</v>
       </c>
       <c r="M5" t="n">
-        <v>1.5004</v>
+        <v>-2.483</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7554999999999999</v>
+        <v>-0.4415</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7449</v>
+        <v>-2.0415</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.616</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.0801</v>
+        <v>-1.0267</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4641</v>
+        <v>1.0267</v>
       </c>
       <c r="S5" t="n">
-        <v>2.4069</v>
+        <v>0.4417</v>
       </c>
       <c r="T5" t="n">
-        <v>1.3675</v>
+        <v>0.2014</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0394</v>
+        <v>0.2403</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9384</v>
+        <v>-0.1088</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2402</v>
+        <v>-0.1088</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6982</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.6277</v>
+        <v>3.7933</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7276</v>
+        <v>2.0414</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9001</v>
+        <v>1.7519</v>
       </c>
       <c r="G6" t="n">
         <v>1.5258</v>
@@ -922,13 +922,13 @@
         <v>1.4374</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9046999999999999</v>
+        <v>1.0703</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3021</v>
+        <v>0.6159</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6026</v>
+        <v>0.4544</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2402</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. JOHNSON</t>
+          <t>J. RODRIGUEZ JIMENEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.4891</v>
+        <v>3.5093</v>
       </c>
       <c r="E7" t="n">
-        <v>4.8237</v>
+        <v>1.3716</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.3346</v>
+        <v>2.1377</v>
       </c>
       <c r="G7" t="n">
-        <v>3.7978</v>
+        <v>2.8003</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8272</v>
+        <v>0.84</v>
       </c>
       <c r="I7" t="n">
-        <v>2.9707</v>
+        <v>1.9603</v>
       </c>
       <c r="J7" t="n">
-        <v>6.2808</v>
+        <v>1.3213</v>
       </c>
       <c r="K7" t="n">
-        <v>1.2687</v>
+        <v>0.0584</v>
       </c>
       <c r="L7" t="n">
-        <v>5.0122</v>
+        <v>1.2629</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.483</v>
+        <v>1.479</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4415</v>
+        <v>0.7816</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.0415</v>
+        <v>0.6974</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.8214</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0267</v>
+        <v>0.8214</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1999</v>
+        <v>-0.1123</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3216</v>
+        <v>0.0503</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1217</v>
+        <v>-0.1626</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1088</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.1088</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. SOLARIN</t>
+          <t>M. ISSOUF</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3.1896</v>
+        <v>3.1079</v>
       </c>
       <c r="E8" t="n">
-        <v>3.7504</v>
+        <v>1.7959</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5608</v>
+        <v>1.312</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8496</v>
+        <v>1.1835</v>
       </c>
       <c r="H8" t="n">
-        <v>2.5757</v>
+        <v>1.236</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.7261</v>
+        <v>-0.0525</v>
       </c>
       <c r="J8" t="n">
-        <v>2.7432</v>
+        <v>1.0517</v>
       </c>
       <c r="K8" t="n">
-        <v>2.8225</v>
+        <v>1.0122</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0793</v>
+        <v>0.0395</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.8937</v>
+        <v>0.1318</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2468</v>
+        <v>0.2238</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.6468</v>
+        <v>-0.092</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8214</v>
+        <v>0.616</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8214</v>
+        <v>0.616</v>
       </c>
       <c r="S8" t="n">
-        <v>1.5187</v>
+        <v>0.37</v>
       </c>
       <c r="T8" t="n">
-        <v>1.0072</v>
+        <v>0.1549</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5115</v>
+        <v>0.2151</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.9384</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.5893</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.3491</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ JIMENEZ</t>
+          <t>R. GOMEZ BARRAL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.8266</v>
+        <v>2.7165</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9261</v>
+        <v>-2.452</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9006</v>
+        <v>5.1685</v>
       </c>
       <c r="G9" t="n">
-        <v>2.8003</v>
+        <v>0.9121</v>
       </c>
       <c r="H9" t="n">
-        <v>0.84</v>
+        <v>1.47</v>
       </c>
       <c r="I9" t="n">
-        <v>1.9603</v>
+        <v>-0.5579</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3213</v>
+        <v>-0.5883</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0584</v>
+        <v>0.7144</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2629</v>
+        <v>-1.3027</v>
       </c>
       <c r="M9" t="n">
-        <v>1.479</v>
+        <v>1.5004</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7816</v>
+        <v>0.7554999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6974</v>
+        <v>0.7449</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8214</v>
+        <v>-0.616</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-3.0801</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8214</v>
+        <v>2.4641</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.795</v>
+        <v>1.482</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3952</v>
+        <v>0.9762</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3998</v>
+        <v>0.5058</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.9384</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. ISSOUF</t>
+          <t>J. SOLARIN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>2.6302</v>
+        <v>2.6666</v>
       </c>
       <c r="E10" t="n">
-        <v>1.3775</v>
+        <v>3.2274</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2527</v>
+        <v>-0.5608</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1835</v>
+        <v>0.8496</v>
       </c>
       <c r="H10" t="n">
-        <v>1.236</v>
+        <v>2.5757</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0525</v>
+        <v>-1.7261</v>
       </c>
       <c r="J10" t="n">
-        <v>1.0517</v>
+        <v>2.7432</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0122</v>
+        <v>2.8225</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0395</v>
+        <v>-0.0793</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1318</v>
+        <v>-1.8937</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2238</v>
+        <v>-0.2468</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.092</v>
+        <v>-1.6468</v>
       </c>
       <c r="P10" t="n">
-        <v>0.616</v>
+        <v>0.8214</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.616</v>
+        <v>0.8214</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1077</v>
+        <v>0.9957</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2635</v>
+        <v>0.4842</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1558</v>
+        <v>0.5115</v>
       </c>
       <c r="V10" t="n">
-        <v>0.9384</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5893</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3491</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>2.3693</v>
+        <v>1.8463</v>
       </c>
       <c r="E11" t="n">
-        <v>3.3194</v>
+        <v>2.7964</v>
       </c>
       <c r="F11" t="n">
         <v>-0.9500999999999999</v>
@@ -1312,10 +1312,10 @@
         <v>1.0267</v>
       </c>
       <c r="S11" t="n">
-        <v>1.5187</v>
+        <v>0.9957</v>
       </c>
       <c r="T11" t="n">
-        <v>1.0731</v>
+        <v>0.5501</v>
       </c>
       <c r="U11" t="n">
         <v>0.4457</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.0397</v>
+        <v>1.0355</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.0884</v>
+        <v>-1.2705</v>
       </c>
       <c r="F12" t="n">
-        <v>2.1281</v>
+        <v>2.306</v>
       </c>
       <c r="G12" t="n">
         <v>-0.2605</v>
@@ -1390,13 +1390,13 @@
         <v>1.6427</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6842</v>
+        <v>0.68</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8018999999999999</v>
+        <v>0.6198</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1177</v>
+        <v>0.0602</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2886</v>
+        <v>0.8824</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.6012999999999999</v>
+        <v>-0.1558</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8899</v>
+        <v>1.0381</v>
       </c>
       <c r="G13" t="n">
         <v>1.3215</v>
@@ -1468,13 +1468,13 @@
         <v>1.4374</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1724</v>
+        <v>0.7662</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2362</v>
+        <v>0.6818</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0638</v>
+        <v>0.0844</v>
       </c>
       <c r="V13" t="n">
         <v>-0.5893</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>40.24060000000001</v>
+        <v>40.89939999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>23.3763</v>
+        <v>24.0349</v>
       </c>
       <c r="F14" t="n">
         <v>16.8643</v>
@@ -1528,13 +1528,13 @@
         <v>12.6407</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.9664</v>
+        <v>-1.966400000000001</v>
       </c>
       <c r="N14" t="n">
         <v>2.5436</v>
       </c>
       <c r="O14" t="n">
-        <v>-4.5098</v>
+        <v>-4.509799999999999</v>
       </c>
       <c r="P14" t="n">
         <v>5.133599999999999</v>
@@ -1546,13 +1546,13 @@
         <v>16.4274</v>
       </c>
       <c r="S14" t="n">
-        <v>8.504399999999999</v>
+        <v>9.1632</v>
       </c>
       <c r="T14" t="n">
-        <v>4.8999</v>
+        <v>5.5585</v>
       </c>
       <c r="U14" t="n">
-        <v>3.6046</v>
+        <v>3.6047</v>
       </c>
       <c r="V14" t="n">
         <v>4.846</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2489</v>
+        <v>0.5463</v>
       </c>
       <c r="E15" t="n">
-        <v>1.263</v>
+        <v>0.5306999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0141</v>
+        <v>0.0156</v>
       </c>
       <c r="G15" t="n">
         <v>-0.2314</v>
@@ -1624,13 +1624,13 @@
         <v>0.2053</v>
       </c>
       <c r="S15" t="n">
-        <v>1.275</v>
+        <v>0.5724</v>
       </c>
       <c r="T15" t="n">
-        <v>1.263</v>
+        <v>0.5306999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.012</v>
+        <v>0.0417</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. LIBROIA</t>
+          <t>R. UKAWUBA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.7056</v>
+        <v>-0.8806</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8933</v>
+        <v>-0.95</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.5989</v>
+        <v>0.0694</v>
       </c>
       <c r="G16" t="n">
-        <v>0.605</v>
+        <v>-2.0853</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.3656</v>
+        <v>-1.1485</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9706</v>
+        <v>-0.9368</v>
       </c>
       <c r="J16" t="n">
-        <v>3.9426</v>
+        <v>-0.8491</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3251</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>3.6175</v>
+        <v>-0.1713</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.3376</v>
+        <v>-1.2362</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.6907</v>
+        <v>-0.4706</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.6468</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.2321</v>
+        <v>0.8214</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2588</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.0267</v>
+        <v>0.8214</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9081</v>
+        <v>-0.0746</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2094</v>
+        <v>-0.1008</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6987</v>
+        <v>0.0262</v>
       </c>
       <c r="V16" t="n">
-        <v>0.8295</v>
+        <v>0.4579</v>
       </c>
       <c r="W16" t="n">
-        <v>1.4189</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5893</v>
+        <v>0.4579</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. UKAWUBA</t>
+          <t>A. LIBROIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.3287</v>
+        <v>-0.9986</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3684</v>
+        <v>2.5795</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0397</v>
+        <v>-3.578</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.0853</v>
+        <v>0.605</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.1485</v>
+        <v>-1.3656</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9368</v>
+        <v>1.9706</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.8491</v>
+        <v>3.9426</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0.3251</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.1713</v>
+        <v>3.6175</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2362</v>
+        <v>-3.3376</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4706</v>
+        <v>-1.6907</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7655999999999999</v>
+        <v>-1.6468</v>
       </c>
       <c r="P17" t="n">
-        <v>0.8214</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.2588</v>
       </c>
       <c r="R17" t="n">
-        <v>0.8214</v>
+        <v>1.0267</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5227000000000001</v>
+        <v>-1.201</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5192</v>
+        <v>-0.5232</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0034</v>
+        <v>-0.6778</v>
       </c>
       <c r="V17" t="n">
-        <v>0.4579</v>
+        <v>0.8295</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.4189</v>
       </c>
       <c r="X17" t="n">
-        <v>0.4579</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="18">
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.6126</v>
+        <v>-1.508</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8393</v>
+        <v>-0.7347</v>
       </c>
       <c r="F18" t="n">
         <v>-0.7733</v>
@@ -1858,10 +1858,10 @@
         <v>0.2053</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2635</v>
+        <v>-0.1589</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.124</v>
+        <v>-0.0194</v>
       </c>
       <c r="U18" t="n">
         <v>-0.1395</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7396</v>
+        <v>-1.5147</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7705</v>
+        <v>-1.4567</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0309</v>
+        <v>-0.058</v>
       </c>
       <c r="G19" t="n">
         <v>-0.9093</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1965</v>
+        <v>0.4214</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0659</v>
+        <v>0.2479</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2623</v>
+        <v>0.1734</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.8079</v>
+        <v>-2.3563</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.17</v>
+        <v>-0.0654</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.6379</v>
+        <v>-2.2909</v>
       </c>
       <c r="G20" t="n">
         <v>0.6306</v>
@@ -2014,13 +2014,13 @@
         <v>1.2321</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.2599</v>
+        <v>-1.8083</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9145</v>
+        <v>-0.8099</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.3454</v>
+        <v>-0.9985000000000001</v>
       </c>
       <c r="V20" t="n">
         <v>-1.1786</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0778</v>
+        <v>-3.6856</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4681</v>
+        <v>-0.3635</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.6098</v>
+        <v>-3.3221</v>
       </c>
       <c r="G21" t="n">
         <v>-1.8473</v>
@@ -2092,13 +2092,13 @@
         <v>0.8214</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.6679</v>
+        <v>-1.2757</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5774</v>
+        <v>-0.4728</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.0906</v>
+        <v>-0.8028999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>-1.1786</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0991</v>
+        <v>-4.4425</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7713</v>
+        <v>-3.0852</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3278</v>
+        <v>-1.3574</v>
       </c>
       <c r="G22" t="n">
         <v>-4.0479</v>
@@ -2170,13 +2170,13 @@
         <v>1.2321</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3328</v>
+        <v>-0.0107</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1122</v>
+        <v>-0.2016</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2205</v>
+        <v>0.1909</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5893</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.2144</v>
+        <v>-4.7044</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.5317</v>
+        <v>-4.6364</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3173</v>
+        <v>-0.068</v>
       </c>
       <c r="G23" t="n">
         <v>-2.0514</v>
@@ -2248,13 +2248,13 @@
         <v>1.0267</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3359</v>
+        <v>-0.154</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0464</v>
+        <v>-0.0582</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2896</v>
+        <v>-0.0958</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2402</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. IKPEZE</t>
+          <t>A. HARO VAL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.5358</v>
+        <v>-6.3199</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.5126</v>
+        <v>-4.3282</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.0232</v>
+        <v>-1.9917</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.3684</v>
+        <v>-4.4249</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.1216</v>
+        <v>-1.5248</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.2468</v>
+        <v>-2.9001</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2505</v>
+        <v>-0.6897</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0137</v>
+        <v>-0.11</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2368</v>
+        <v>-0.5797</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.6188</v>
+        <v>-3.7352</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.1352</v>
+        <v>-1.4148</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.4836</v>
+        <v>-2.3204</v>
       </c>
       <c r="P24" t="n">
-        <v>0.8214</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.0267</v>
+        <v>-3.0801</v>
       </c>
       <c r="R24" t="n">
         <v>1.8481</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.7404</v>
+        <v>-0.5541</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7364000000000001</v>
+        <v>-0.4496</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.004</v>
+        <v>-0.1045</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.2484</v>
+        <v>-0.1088</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>-0.1088</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.2484</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A. HARO VAL</t>
+          <t>A. IKPEZE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.9615</v>
+        <v>-6.7695</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.8513</v>
+        <v>-1.8264</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.1102</v>
+        <v>-4.943</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.4249</v>
+        <v>-3.3684</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.5248</v>
+        <v>-2.1216</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.9001</v>
+        <v>-1.2468</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.6897</v>
+        <v>0.2505</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.11</v>
+        <v>0.0137</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.5797</v>
+        <v>0.2368</v>
       </c>
       <c r="M25" t="n">
-        <v>-3.7352</v>
+        <v>-3.6188</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.4148</v>
+        <v>-2.1352</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.3204</v>
+        <v>-1.4836</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.2321</v>
+        <v>0.8214</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.0801</v>
+        <v>-1.0267</v>
       </c>
       <c r="R25" t="n">
         <v>1.8481</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.1957</v>
+        <v>-1.974</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9726</v>
+        <v>-1.0502</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2231</v>
+        <v>-0.9238</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.1088</v>
+        <v>-2.2484</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.1088</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-2.2484</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.4065</v>
+        <v>-6.9096</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.7374</v>
+        <v>-2.5282</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.6691</v>
+        <v>-4.3814</v>
       </c>
       <c r="G26" t="n">
         <v>-3.4988</v>
@@ -2482,13 +2482,13 @@
         <v>1.0267</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.0864</v>
+        <v>-1.5895</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.9068000000000001</v>
+        <v>-0.6975</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.1796</v>
+        <v>-0.8919</v>
       </c>
       <c r="V26" t="n">
         <v>-0.5893</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-40.2406</v>
+        <v>-39.5434</v>
       </c>
       <c r="E27" t="n">
-        <v>-16.8643</v>
+        <v>-16.8645</v>
       </c>
       <c r="F27" t="n">
-        <v>-23.3764</v>
+        <v>-22.6788</v>
       </c>
       <c r="G27" t="n">
         <v>-21.7568</v>
@@ -2530,10 +2530,10 @@
         <v>-13.6262</v>
       </c>
       <c r="I27" t="n">
-        <v>-8.130600000000001</v>
+        <v>-8.130599999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>1.966500000000001</v>
+        <v>1.9665</v>
       </c>
       <c r="K27" t="n">
         <v>-2.5435</v>
@@ -2551,7 +2551,7 @@
         <v>-12.6405</v>
       </c>
       <c r="P27" t="n">
-        <v>-5.133799999999999</v>
+        <v>-5.133800000000001</v>
       </c>
       <c r="Q27" t="n">
         <v>-16.4274</v>
@@ -2560,16 +2560,16 @@
         <v>11.2939</v>
       </c>
       <c r="S27" t="n">
-        <v>-8.5044</v>
+        <v>-7.807</v>
       </c>
       <c r="T27" t="n">
         <v>-3.6046</v>
       </c>
       <c r="U27" t="n">
-        <v>-4.8999</v>
+        <v>-4.2025</v>
       </c>
       <c r="V27" t="n">
-        <v>-4.8458</v>
+        <v>-4.845800000000001</v>
       </c>
       <c r="W27" t="n">
         <v>1.2012</v>
